--- a/胎壓檢測器資料庫_V10/BYD_Data.xlsx
+++ b/胎壓檢測器資料庫_V10/BYD_Data.xlsx
@@ -1713,17 +1713,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>03/2025 -</t>
+          <t>03/2025 -, 04/2025 -</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Faraday 3319</t>
+          <t>Faraday 3319, SENS 7 Gen2 inkl. RDV036, SENS 7 Gen2 inkl. RDV037, SENS 7 Gen2 inkl. RDV038, SENS 7 Gen2 inkl. RDV043</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SCHRADER</t>
+          <t>SCHRADER, PLATIN</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
